--- a/测试结果.xlsx
+++ b/测试结果.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="13980"/>
+    <workbookView windowWidth="29400" windowHeight="12320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>eog</t>
   </si>
@@ -265,6 +265,147 @@
   }
 }</t>
   </si>
+  <si>
+    <t>clean+direct</t>
+  </si>
+  <si>
+    <t>{
+"RRMSE_temporal": {
+"mean": 0.2532206954591108,
+"std": 0.11949514944405706
+},
+"RRMSE_spectral": {
+"mean": 0.2586408467567732,
+"std": 0.13983953256471338
+},
+"CC": {
+"mean": 0.9603097662329674,
+"std": 0.04172686937007867
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"RRMSE_temporal": {
+"mean": 0.5141092124271446,
+"std": 0.15733971066035277
+},
+"RRMSE_spectral": {
+"mean": 0.4464455750169216,
+"std": 0.1946396165599048
+},
+"CC": {
+"mean": 0.8527903475010201,
+"std": 0.09044989362488526
+}
+}</t>
+  </si>
+  <si>
+    <t>clean+residual</t>
+  </si>
+  <si>
+    <t>{
+"RRMSE_temporal": {
+"mean": 0.2515819613574551,
+"std": 0.11899455025766882
+},
+"RRMSE_spectral": {
+"mean": 0.2575854214056667,
+"std": 0.13798532563679375
+},
+"CC": {
+"mean": 0.9610600738662534,
+"std": 0.04038685347487988
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"RRMSE_temporal": {
+"mean": 0.5289452090985788,
+"std": 0.15753150141168215
+},
+"RRMSE_spectral": {
+"mean": 0.4594619867685842,
+"std": 0.18320416271699436
+},
+"CC": {
+"mean": 0.8443347206586493,
+"std": 0.09256139084669697
+}
+}</t>
+  </si>
+  <si>
+    <t>clean+mix</t>
+  </si>
+  <si>
+    <t>{
+"RRMSE_temporal": {
+"mean": 0.2566808713665974,
+"std": 0.11711044370572607
+},
+"RRMSE_spectral": {
+"mean": 0.2658366468454818,
+"std": 0.14130587036554754
+},
+"CC": {
+"mean": 0.9597270107638519,
+"std": 0.04087375556763663
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"RRMSE_temporal": {
+"mean": 0.5115797005450919,
+"std": 0.15476769612932104
+},
+"RRMSE_spectral": {
+"mean": 0.43688945347102565,
+"std": 0.18573918859109753
+},
+"CC": {
+"mean": 0.8549818843163571,
+"std": 0.08826318772320763
+}
+}</t>
+  </si>
+  <si>
+    <t>clean-mix-vel</t>
+  </si>
+  <si>
+    <t>{
+"RRMSE_temporal": {
+"mean": 0.5670139833361701,
+"std": 0.11553040579938459
+},
+"RRMSE_spectral": {
+"mean": 0.5988842157960201,
+"std": 0.17306915465903938
+},
+"CC": {
+"mean": 0.8298426911037052,
+"std": 0.0674936513098005
+}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "RRMSE_temporal": {
+    "mean": 0.6507582444159155,
+    "std": 0.22001545160586794
+  },
+  "RRMSE_spectral": {
+    "mean": 0.6515373246535483,
+    "std": 0.49293419702412844
+  },
+  "CC": {
+    "mean": 0.7900938624708438,
+    "std": 0.11385488981279203
+  }
+}
+</t>
+  </si>
 </sst>
 </file>
 
@@ -623,12 +764,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -755,7 +911,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -767,34 +923,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -879,11 +1035,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1411,7 +1570,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="16.3461538461538" style="1" customWidth="1"/>
@@ -1505,9 +1664,48 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1">
-        <v>7</v>
+    <row r="9" ht="236" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" ht="236.75" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" ht="236.75" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" ht="252.75" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
